--- a/Luban/Config/Datas/#SeasonConfig.xlsx
+++ b/Luban/Config/Datas/#SeasonConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8361BC0A-68F4-463D-AD94-78D6A0B0EEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F86E402-9A58-4A9C-A397-BD42F2C66D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13860" yWindow="6270" windowWidth="28800" windowHeight="14220" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView minimized="1" xWindow="2550" yWindow="2550" windowWidth="35565" windowHeight="9315" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +74,54 @@
   </si>
   <si>
     <t>季节类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Night</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Morning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunrise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早晨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>88</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -484,7 +532,7 @@
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,8 +542,20 @@
       <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -505,8 +565,20 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -516,74 +588,158 @@
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="3">
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
